--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.62068891649886</v>
+      </c>
+      <c r="C2">
         <v>32.20566813761192</v>
-      </c>
-      <c r="C2">
-        <v>25.62068891649886</v>
       </c>
       <c r="D2">
         <v>3.105043484044764</v>
       </c>
       <c r="E2">
-        <v>20.40576031706175</v>
+        <v>16.23346657346644</v>
       </c>
       <c r="F2">
         <v>63.36077310947181</v>
       </c>
       <c r="G2">
-        <v>16.23346657346644</v>
+        <v>20.40576031706175</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.98640517049254</v>
+      </c>
+      <c r="C3">
         <v>27.98083351905505</v>
-      </c>
-      <c r="C3">
-        <v>27.98640517049254</v>
       </c>
       <c r="D3">
         <v>3.573874950219036</v>
       </c>
       <c r="E3">
-        <v>17.94019933554817</v>
+        <v>17.94377165720002</v>
       </c>
       <c r="F3">
         <v>64.11602900725181</v>
       </c>
       <c r="G3">
-        <v>17.94377165720002</v>
+        <v>17.94019933554817</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>26.38099983391463</v>
+      </c>
+      <c r="C4">
         <v>27.52698887228035</v>
-      </c>
-      <c r="C4">
-        <v>26.38099983391463</v>
       </c>
       <c r="D4">
         <v>3.632798358875347</v>
       </c>
       <c r="E4">
-        <v>17.88535416756593</v>
+        <v>17.1407605645962</v>
       </c>
       <c r="F4">
         <v>64.97388526783787</v>
       </c>
       <c r="G4">
-        <v>17.14076056459619</v>
+        <v>17.88535416756593</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.34125269978402</v>
+      </c>
+      <c r="C5">
         <v>29.80561555075594</v>
-      </c>
-      <c r="C5">
-        <v>34.34125269978402</v>
       </c>
       <c r="D5">
         <v>3.355072463768116</v>
       </c>
       <c r="E5">
-        <v>18.1578947368421</v>
+        <v>20.92105263157895</v>
       </c>
       <c r="F5">
         <v>60.92105263157895</v>
       </c>
       <c r="G5">
-        <v>20.92105263157895</v>
+        <v>18.1578947368421</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.64536453645365</v>
+      </c>
+      <c r="C6">
         <v>34.83348334833483</v>
-      </c>
-      <c r="C6">
-        <v>33.64536453645365</v>
       </c>
       <c r="D6">
         <v>2.870801033591731</v>
       </c>
       <c r="E6">
-        <v>20.67528582113474</v>
+        <v>19.9700822737472</v>
       </c>
       <c r="F6">
         <v>59.35463190511807</v>
       </c>
       <c r="G6">
-        <v>19.9700822737472</v>
+        <v>20.67528582113474</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>31.23647771527477</v>
+      </c>
+      <c r="C7">
         <v>30.3926871484206</v>
-      </c>
-      <c r="C7">
-        <v>31.23647771527477</v>
       </c>
       <c r="D7">
         <v>3.290265171738743</v>
       </c>
       <c r="E7">
+        <v>19.3260156616023</v>
+      </c>
+      <c r="F7">
+        <v>61.87002208687505</v>
+      </c>
+      <c r="G7">
         <v>18.80396225152266</v>
-      </c>
-      <c r="F7">
-        <v>61.87002208687503</v>
-      </c>
-      <c r="G7">
-        <v>19.3260156616023</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>25.18986910114823</v>
+      </c>
+      <c r="C8">
         <v>33.97719135005578</v>
-      </c>
-      <c r="C8">
-        <v>25.18986910114823</v>
       </c>
       <c r="D8">
         <v>2.943150861698162</v>
       </c>
       <c r="E8">
-        <v>21.34687368965528</v>
+        <v>15.82605661607397</v>
       </c>
       <c r="F8">
         <v>62.82706969427075</v>
       </c>
       <c r="G8">
-        <v>15.82605661607397</v>
+        <v>21.34687368965528</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>34.54960091220068</v>
+      </c>
+      <c r="C9">
         <v>15.71645762067655</v>
-      </c>
-      <c r="C9">
-        <v>34.54960091220068</v>
       </c>
       <c r="D9">
         <v>6.362756952841596</v>
       </c>
       <c r="E9">
-        <v>10.45908688503857</v>
+        <v>22.99228531680789</v>
       </c>
       <c r="F9">
         <v>66.54862779815353</v>
       </c>
       <c r="G9">
-        <v>22.99228531680789</v>
+        <v>10.45908688503857</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.32037957523724</v>
+      </c>
+      <c r="C10">
         <v>28.81156800723</v>
-      </c>
-      <c r="C10">
-        <v>27.32037957523724</v>
       </c>
       <c r="D10">
         <v>3.470828105395232</v>
       </c>
       <c r="E10">
-        <v>18.4533456818708</v>
+        <v>17.49826348691827</v>
       </c>
       <c r="F10">
         <v>64.04839083121092</v>
       </c>
       <c r="G10">
-        <v>17.49826348691827</v>
+        <v>18.4533456818708</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>33.11217084801991</v>
+      </c>
+      <c r="C11">
         <v>24.79784366576819</v>
-      </c>
-      <c r="C11">
-        <v>33.11217084801991</v>
       </c>
       <c r="D11">
         <v>4.032608695652174</v>
       </c>
       <c r="E11">
-        <v>15.70378151260504</v>
+        <v>20.96901260504202</v>
       </c>
       <c r="F11">
         <v>63.32720588235294</v>
       </c>
       <c r="G11">
-        <v>20.96901260504202</v>
+        <v>15.70378151260504</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>30.81778650582129</v>
+      </c>
+      <c r="C12">
         <v>25.96437087950624</v>
-      </c>
-      <c r="C12">
-        <v>30.81778650582129</v>
       </c>
       <c r="D12">
         <v>3.851431658562939</v>
       </c>
       <c r="E12">
-        <v>16.56079448868212</v>
+        <v>19.65643732665295</v>
       </c>
       <c r="F12">
         <v>63.78276818466494</v>
       </c>
       <c r="G12">
-        <v>19.65643732665295</v>
+        <v>16.56079448868212</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.50315585046124</v>
+      </c>
+      <c r="C13">
         <v>27.75530021039003</v>
-      </c>
-      <c r="C13">
-        <v>29.50315585046124</v>
       </c>
       <c r="D13">
         <v>3.602915451895044</v>
       </c>
       <c r="E13">
-        <v>17.64948029227128</v>
+        <v>18.76093444478748</v>
       </c>
       <c r="F13">
         <v>63.58958526294123</v>
       </c>
       <c r="G13">
-        <v>18.76093444478748</v>
+        <v>17.64948029227128</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.53267293765088</v>
+      </c>
+      <c r="C14">
         <v>30.34212935986015</v>
-      </c>
-      <c r="C14">
-        <v>27.53267293765088</v>
       </c>
       <c r="D14">
         <v>3.295747599451303</v>
       </c>
       <c r="E14">
+        <v>17.4395613086921</v>
+      </c>
+      <c r="F14">
+        <v>63.34133031030029</v>
+      </c>
+      <c r="G14">
         <v>19.21910838100762</v>
-      </c>
-      <c r="F14">
-        <v>63.34133031030027</v>
-      </c>
-      <c r="G14">
-        <v>17.4395613086921</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.91618185735833</v>
+      </c>
+      <c r="C15">
         <v>28.39186956834016</v>
-      </c>
-      <c r="C15">
-        <v>28.91618185735833</v>
       </c>
       <c r="D15">
         <v>3.522135087275487</v>
       </c>
       <c r="E15">
-        <v>18.04858003835266</v>
+        <v>18.38188293306548</v>
       </c>
       <c r="F15">
         <v>63.56953702858186</v>
       </c>
       <c r="G15">
-        <v>18.38188293306548</v>
+        <v>18.04858003835266</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.3088313061872</v>
+      </c>
+      <c r="C16">
         <v>32.70756213643575</v>
-      </c>
-      <c r="C16">
-        <v>26.3088313061872</v>
       </c>
       <c r="D16">
         <v>3.057396928051738</v>
       </c>
       <c r="E16">
+        <v>16.54472896574659</v>
+      </c>
+      <c r="F16">
+        <v>62.88659793814433</v>
+      </c>
+      <c r="G16">
         <v>20.56867309610908</v>
-      </c>
-      <c r="F16">
-        <v>62.88659793814434</v>
-      </c>
-      <c r="G16">
-        <v>16.54472896574659</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>28.4036047634374</v>
+      </c>
+      <c r="C17">
         <v>33.1509494689411</v>
-      </c>
-      <c r="C17">
-        <v>28.4036047634374</v>
       </c>
       <c r="D17">
         <v>3.016504854368932</v>
       </c>
       <c r="E17">
-        <v>20.51997210877577</v>
+        <v>17.58143241358701</v>
       </c>
       <c r="F17">
         <v>61.89859547763722</v>
       </c>
       <c r="G17">
-        <v>17.58143241358701</v>
+        <v>20.51997210877578</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.52062868369352</v>
+      </c>
+      <c r="C18">
         <v>32.4950884086444</v>
-      </c>
-      <c r="C18">
-        <v>25.52062868369352</v>
       </c>
       <c r="D18">
         <v>3.07738814993954</v>
       </c>
       <c r="E18">
-        <v>20.56446599527539</v>
+        <v>16.15069004102947</v>
       </c>
       <c r="F18">
         <v>63.28484396369514</v>
       </c>
       <c r="G18">
-        <v>16.15069004102947</v>
+        <v>20.56446599527539</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>26.5887388870596</v>
+      </c>
+      <c r="C19">
         <v>29.53407968389858</v>
-      </c>
-      <c r="C19">
-        <v>26.5887388870596</v>
       </c>
       <c r="D19">
         <v>3.385918947544456</v>
       </c>
       <c r="E19">
-        <v>18.9172088707041</v>
+        <v>17.03065517932278</v>
       </c>
       <c r="F19">
         <v>64.05213594997311</v>
       </c>
       <c r="G19">
-        <v>17.03065517932278</v>
+        <v>18.9172088707041</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>29.55982490272374</v>
+      </c>
+      <c r="C20">
         <v>31.08280642023346</v>
-      </c>
-      <c r="C20">
-        <v>29.55982490272374</v>
       </c>
       <c r="D20">
         <v>3.21721271393643</v>
       </c>
       <c r="E20">
-        <v>19.34903964424259</v>
+        <v>18.4009840098401</v>
       </c>
       <c r="F20">
         <v>62.24997634591731</v>
       </c>
       <c r="G20">
-        <v>18.4009840098401</v>
+        <v>19.34903964424259</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>30.79930495221547</v>
+      </c>
+      <c r="C21">
         <v>28.14943527367507</v>
-      </c>
-      <c r="C21">
-        <v>30.79930495221547</v>
       </c>
       <c r="D21">
         <v>3.552469135802469</v>
       </c>
       <c r="E21">
-        <v>17.70975676414321</v>
+        <v>19.37687892866904</v>
       </c>
       <c r="F21">
         <v>62.91336430718776</v>
       </c>
       <c r="G21">
-        <v>19.37687892866904</v>
+        <v>17.70975676414321</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>30.18544182670098</v>
+      </c>
+      <c r="C22">
         <v>25.94205767834752</v>
-      </c>
-      <c r="C22">
-        <v>30.18544182670098</v>
       </c>
       <c r="D22">
         <v>3.85474433986263</v>
       </c>
       <c r="E22">
-        <v>16.61594386676812</v>
+        <v>19.33384056133232</v>
       </c>
       <c r="F22">
         <v>64.05021557189957</v>
       </c>
       <c r="G22">
-        <v>19.33384056133232</v>
+        <v>16.61594386676812</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.56018931339598</v>
+      </c>
+      <c r="C23">
         <v>33.05439330543933</v>
-      </c>
-      <c r="C23">
-        <v>27.56018931339598</v>
       </c>
       <c r="D23">
         <v>3.025316455696203</v>
       </c>
       <c r="E23">
+        <v>17.15920737956953</v>
+      </c>
+      <c r="F23">
+        <v>62.26084728390844</v>
+      </c>
+      <c r="G23">
         <v>20.57994533652203</v>
-      </c>
-      <c r="F23">
-        <v>62.26084728390843</v>
-      </c>
-      <c r="G23">
-        <v>17.15920737956953</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.65298476396637</v>
+      </c>
+      <c r="C24">
         <v>30.07909416368329</v>
-      </c>
-      <c r="C24">
-        <v>27.65298476396637</v>
       </c>
       <c r="D24">
         <v>3.324568201948627</v>
       </c>
       <c r="E24">
-        <v>19.0697379811245</v>
+        <v>17.53161750733695</v>
       </c>
       <c r="F24">
         <v>63.39864451153854</v>
       </c>
       <c r="G24">
-        <v>17.53161750733695</v>
+        <v>19.0697379811245</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.9090283354365</v>
+      </c>
+      <c r="C25">
         <v>45.14167718251692</v>
-      </c>
-      <c r="C25">
-        <v>28.9090283354365</v>
       </c>
       <c r="D25">
         <v>2.215247776365947</v>
       </c>
       <c r="E25">
-        <v>25.93593461639863</v>
+        <v>16.60954389665172</v>
       </c>
       <c r="F25">
         <v>57.45452148694964</v>
       </c>
       <c r="G25">
-        <v>16.60954389665173</v>
+        <v>25.93593461639863</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>32.19957937486402</v>
+      </c>
+      <c r="C26">
         <v>38.87881644789325</v>
-      </c>
-      <c r="C26">
-        <v>32.19957937486402</v>
       </c>
       <c r="D26">
         <v>2.572094758440589</v>
       </c>
       <c r="E26">
-        <v>22.72573124205172</v>
+        <v>18.82153454853752</v>
       </c>
       <c r="F26">
         <v>58.45273420941076</v>
       </c>
       <c r="G26">
-        <v>18.82153454853752</v>
+        <v>22.72573124205172</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>30.95948827292111</v>
+      </c>
+      <c r="C27">
         <v>46.13006396588486</v>
-      </c>
-      <c r="C27">
-        <v>30.95948827292111</v>
       </c>
       <c r="D27">
         <v>2.167783683845621</v>
       </c>
       <c r="E27">
-        <v>26.04900367226536</v>
+        <v>17.48239118656312</v>
       </c>
       <c r="F27">
         <v>56.46860514117152</v>
       </c>
       <c r="G27">
-        <v>17.48239118656312</v>
+        <v>26.04900367226536</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>31.01391650099404</v>
+      </c>
+      <c r="C28">
         <v>51.31875414181577</v>
-      </c>
-      <c r="C28">
-        <v>31.01391650099404</v>
       </c>
       <c r="D28">
         <v>1.948605371900826</v>
       </c>
       <c r="E28">
+        <v>17.0095224249473</v>
+      </c>
+      <c r="F28">
+        <v>54.84480628043904</v>
+      </c>
+      <c r="G28">
         <v>28.14567129461365</v>
-      </c>
-      <c r="F28">
-        <v>54.84480628043905</v>
-      </c>
-      <c r="G28">
-        <v>17.0095224249473</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>27.31681740726176</v>
+      </c>
+      <c r="C29">
         <v>31.62930921483812</v>
-      </c>
-      <c r="C29">
-        <v>27.31681740726176</v>
       </c>
       <c r="D29">
         <v>3.161624533775383</v>
       </c>
       <c r="E29">
-        <v>19.89938974105229</v>
+        <v>17.18621144647864</v>
       </c>
       <c r="F29">
         <v>62.91439881246907</v>
       </c>
       <c r="G29">
-        <v>17.18621144647864</v>
+        <v>19.89938974105229</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>28.48871092060985</v>
+      </c>
+      <c r="C30">
         <v>26.08049931381949</v>
-      </c>
-      <c r="C30">
-        <v>28.48871092060985</v>
       </c>
       <c r="D30">
         <v>3.834282419087436</v>
       </c>
       <c r="E30">
-        <v>16.8730235952323</v>
+        <v>18.43103867672099</v>
       </c>
       <c r="F30">
         <v>64.6959377280467</v>
       </c>
       <c r="G30">
-        <v>18.43103867672099</v>
+        <v>16.8730235952323</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.13637365058383</v>
+      </c>
+      <c r="C31">
         <v>30.31504736726151</v>
-      </c>
-      <c r="C31">
-        <v>29.13637365058383</v>
       </c>
       <c r="D31">
         <v>3.298691860465116</v>
       </c>
       <c r="E31">
-        <v>19.01208981001727</v>
+        <v>18.27288428324698</v>
       </c>
       <c r="F31">
         <v>62.71502590673575</v>
       </c>
       <c r="G31">
-        <v>18.27288428324698</v>
+        <v>19.01208981001727</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.00538160469667</v>
+      </c>
+      <c r="C32">
         <v>29.04231898238748</v>
-      </c>
-      <c r="C32">
-        <v>31.00538160469667</v>
       </c>
       <c r="D32">
         <v>3.443251210781217</v>
       </c>
       <c r="E32">
-        <v>18.14603950938061</v>
+        <v>19.37258797906079</v>
       </c>
       <c r="F32">
         <v>62.48137251155859</v>
       </c>
       <c r="G32">
-        <v>19.37258797906079</v>
+        <v>18.14603950938061</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.36412078152753</v>
+      </c>
+      <c r="C33">
         <v>25.47069271758437</v>
-      </c>
-      <c r="C33">
-        <v>25.36412078152753</v>
       </c>
       <c r="D33">
         <v>3.926080892608089</v>
       </c>
       <c r="E33">
-        <v>16.88648139425342</v>
+        <v>16.81582666038625</v>
       </c>
       <c r="F33">
         <v>66.29769194536034</v>
       </c>
       <c r="G33">
-        <v>16.81582666038625</v>
+        <v>16.88648139425342</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>28.78057820607858</v>
+      </c>
+      <c r="C34">
         <v>32.95033358042995</v>
-      </c>
-      <c r="C34">
-        <v>28.78057820607858</v>
       </c>
       <c r="D34">
         <v>3.034870641169854</v>
       </c>
       <c r="E34">
-        <v>20.37355334020855</v>
+        <v>17.79534777128452</v>
       </c>
       <c r="F34">
         <v>61.83109888850693</v>
       </c>
       <c r="G34">
-        <v>17.79534777128452</v>
+        <v>20.37355334020855</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>29.85153764581124</v>
+      </c>
+      <c r="C35">
         <v>28.74867444326617</v>
-      </c>
-      <c r="C35">
-        <v>29.85153764581124</v>
       </c>
       <c r="D35">
         <v>3.478421246772409</v>
       </c>
       <c r="E35">
-        <v>18.12650441294464</v>
+        <v>18.82187750735491</v>
       </c>
       <c r="F35">
         <v>63.05161807970045</v>
       </c>
       <c r="G35">
-        <v>18.82187750735491</v>
+        <v>18.12650441294464</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>25.26470060417539</v>
+      </c>
+      <c r="C36">
         <v>32.35229606588103</v>
-      </c>
-      <c r="C36">
-        <v>25.26470060417539</v>
       </c>
       <c r="D36">
         <v>3.090970724191063</v>
       </c>
       <c r="E36">
-        <v>20.52589298703927</v>
+        <v>16.02917270214367</v>
       </c>
       <c r="F36">
         <v>63.44493431081705</v>
       </c>
       <c r="G36">
-        <v>16.02917270214367</v>
+        <v>20.52589298703927</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>28.18193908764464</v>
+      </c>
+      <c r="C37">
         <v>31.45697566165713</v>
-      </c>
-      <c r="C37">
-        <v>28.18193908764464</v>
       </c>
       <c r="D37">
         <v>3.178945143219533</v>
       </c>
       <c r="E37">
-        <v>19.70507987420074</v>
+        <v>17.65355216295587</v>
       </c>
       <c r="F37">
-        <v>62.6413679628434</v>
+        <v>62.64136796284339</v>
       </c>
       <c r="G37">
-        <v>17.65355216295587</v>
+        <v>19.70507987420073</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>29.2396604659563</v>
+      </c>
+      <c r="C38">
         <v>37.61964962976341</v>
-      </c>
-      <c r="C38">
-        <v>29.2396604659563</v>
       </c>
       <c r="D38">
         <v>2.658185309649544</v>
       </c>
       <c r="E38">
-        <v>22.54573005736551</v>
+        <v>17.5235415088213</v>
       </c>
       <c r="F38">
         <v>59.93072843381318</v>
       </c>
       <c r="G38">
-        <v>17.5235415088213</v>
+        <v>22.54573005736551</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>28.45208523990064</v>
+      </c>
+      <c r="C39">
         <v>29.85096090992286</v>
-      </c>
-      <c r="C39">
-        <v>28.45208523990064</v>
       </c>
       <c r="D39">
         <v>3.34997591205711</v>
       </c>
       <c r="E39">
-        <v>18.85684554779248</v>
+        <v>17.97317608972136</v>
       </c>
       <c r="F39">
         <v>63.16997836248617</v>
       </c>
       <c r="G39">
-        <v>17.97317608972136</v>
+        <v>18.85684554779248</v>
       </c>
     </row>
   </sheetData>
